--- a/Design/booster.xlsx
+++ b/Design/booster.xlsx
@@ -5,26 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hardware\73_PFS122\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hardware\74_Splinter\Splinter\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BC5F12-78D6-4E4D-AD07-0DE497208F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE5FBAF-CC6C-40CA-8AB1-7D7ACC33CC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{E1E1ECF7-BCFE-4D5D-B303-254501912387}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{E1E1ECF7-BCFE-4D5D-B303-254501912387}"/>
   </bookViews>
   <sheets>
     <sheet name="calc" sheetId="1" r:id="rId1"/>
     <sheet name="V_BOST Sweep" sheetId="2" r:id="rId2"/>
     <sheet name="VPP_VDD" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'V_BOST Sweep'!$B$9:$B$19</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'V_BOST Sweep'!$B$9:$B$29</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'V_BOST Sweep'!$G$5</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'V_BOST Sweep'!$G$9:$G$29</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'V_BOST Sweep'!$P$5</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'V_BOST Sweep'!$P$9:$P$19</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -4014,16 +4006,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>220980</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6477,6 +6469,16 @@
         <v>38</v>
       </c>
     </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="P4">
+        <f>LINEST(Q6:Q41,N6:N41)</f>
+        <v>0.21916473616473608</v>
+      </c>
+      <c r="R4">
+        <f>LINEST(S6:S29,N6:N29)</f>
+        <v>0.52750434782608679</v>
+      </c>
+    </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>C5/47</f>
